--- a/data/XIP_Deal_Funnel_Intake.xlsx
+++ b/data/XIP_Deal_Funnel_Intake.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Deal Funnel" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y37</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y36"/>
+  <dimension ref="A1:Y37"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -3201,10 +3201,87 @@
         <v>2026-09-11T18:49:04Z</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>DF-00036</v>
+      </c>
+      <c r="B37" t="str">
+        <v>2026-09-17T14:41:28Z</v>
+      </c>
+      <c r="C37" t="str">
+        <v>HedgeStone.com - New Business Listings For You - Sep 17th, 2026</v>
+      </c>
+      <c r="D37" t="str">
+        <v>info-hedgestonebusiness.com@shared1.ccsend.com</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Broker</v>
+      </c>
+      <c r="F37" t="str">
+        <v>NYC HVAC &amp; Mechanical Contractor (unnamed; Listing #72856)</v>
+      </c>
+      <c r="G37" t="str">
+        <v>Other infra (HVAC/mechanical contracting - government &amp; public-sector construction)</v>
+      </c>
+      <c r="H37" t="str">
+        <v>New York City</v>
+      </c>
+      <c r="I37" t="str">
+        <v>Unknown (2025 Net Income stated: $175,885)</v>
+      </c>
+      <c r="J37" t="str">
+        <v>$1,585,000 (2025)</v>
+      </c>
+      <c r="K37" t="str">
+        <v>Unknown (2025 Net Income margin ~11%, not EBITDA)</v>
+      </c>
+      <c r="L37" t="str">
+        <v>$3,000,000</v>
+      </c>
+      <c r="M37" t="str">
+        <v>Capex-heavy construction/project contracting (HVAC &amp; mechanical, government/public-sector work; $6.99M awarded 2026 backlog)</v>
+      </c>
+      <c r="N37" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="O37" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="P37" t="str">
+        <v>HedgeStone Business Advisors</v>
+      </c>
+      <c r="Q37" t="str">
+        <v>From HedgeStone.com 'Top 10 New Business Listings' broker digest bundling ~9 unrelated small businesses (restaurants, juice bar, moped shop, laundromat, bridal boutique, PA residential real estate brokerage, etc.); only this listing plausibly fits XIP's infra mandate and was scored, others excluded as out-of-mandate consumer/retail/service businesses. Certifications: MBE, DBE, SBE. NDA/CIM availability not stated.</v>
+      </c>
+      <c r="R37">
+        <v>29</v>
+      </c>
+      <c r="S37" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="T37" t="str">
+        <v>Government/public-sector HVAC &amp; mechanical contractor is infra-adjacent (Other infra) but lands in Pass tier overall given sub-scale financials (~$1.6M revenue, ~$176K net income vs. the $3-20M EBITDA sweet spot), a capex-heavy project-based business model, and no stated management/systems depth.</v>
+      </c>
+      <c r="U37" t="str">
+        <v>N</v>
+      </c>
+      <c r="V37" t="str">
+        <v>https://outlook.office365.com/owa/?ItemID=AAMkAGJiZDg3MTI0LWFhNzUtNGQzYS1hNWQzLWZlNDVmMmExMzRkNgBGAAAAAAD9u3VVtvqtSpWuAIjP80zoBwB5X058TjLSTIlO61qPMaSdAAAAAAEMAAB5X058TjLSTIlO61qPMaSdAAExeXFdAAA%3D&amp;exvsurl=1&amp;viewmodel=ReadMessageItem</v>
+      </c>
+      <c r="W37" t="str">
+        <v>New</v>
+      </c>
+      <c r="X37" t="str">
+        <v>&lt;1142347062212.1123831718610.1046578339.0.741040JL.2002@synd.ccsend.com&gt;</v>
+      </c>
+      <c r="Y37" t="str">
+        <v>2026-09-17T14:50:47Z</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y36"/>
+  <autoFilter ref="A1:Y37"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Y36"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y37"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/XIP_Deal_Funnel_Intake.xlsx
+++ b/data/XIP_Deal_Funnel_Intake.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Deal Funnel" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y38</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y37"/>
+  <dimension ref="A1:Y38"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -3278,10 +3278,87 @@
         <v>2026-09-17T14:50:47Z</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>DF-00037</v>
+      </c>
+      <c r="B38" t="str">
+        <v>2026-09-21T15:08:35Z</v>
+      </c>
+      <c r="C38" t="str">
+        <v>EARLY ACCESS: New Listing 1915, Award-Winning High-End Outdoor Lighting Business with $1.15M Annual Revenue</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Baystate Business Brokers &lt;admin@baystatebusinessbrokers.com&gt;</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Broker</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Northern Outdoor Lighting</v>
+      </c>
+      <c r="G38" t="str">
+        <v>Consumer-facing within mandate — residential/estate outdoor lighting design, installation &amp; service</v>
+      </c>
+      <c r="H38" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="I38" t="str">
+        <v>Unknown (only SDE stated, not EBITDA)</v>
+      </c>
+      <c r="J38" t="str">
+        <v>$1,102,337 (2025)</v>
+      </c>
+      <c r="K38" t="str">
+        <v>Unknown (SDE 2025 $131,696 on $1,102,337 revenue = ~12% SDE margin, not a true EBITDA margin)</v>
+      </c>
+      <c r="L38" t="str">
+        <v>$715,000 (Business Price)</v>
+      </c>
+      <c r="M38" t="str">
+        <v>Mixed — core installations 40-52% of sales ($5K-$75K+ projects), recurring service/tune-ups 18-25%, incremental upgrades 12-20%</v>
+      </c>
+      <c r="N38" t="str">
+        <v>Partial — semi-absentee ownership, General Manager runs daily operations, owner ~5-15 hrs/week strategic oversight; no CFO or ERP/systems mentioned</v>
+      </c>
+      <c r="O38" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="P38" t="str">
+        <v>BayState Business Brokers (John Brice)</v>
+      </c>
+      <c r="Q38" t="str">
+        <v>Broker blast to 'Preferred Buyers' with a one-week early-access window; no NDA/CIM/attachment provided yet, teaser-level detail only. Diverse client base (hundreds of relationships, no concentration risk); demand exceeds current technician capacity.</v>
+      </c>
+      <c r="R38">
+        <v>33</v>
+      </c>
+      <c r="S38" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="T38" t="str">
+        <v>In-mandate but sub-scale residential outdoor-lighting design/install/service business with only ~$132K SDE and a $715K asking price, far below XIP's target EBITDA range, so it scores well under the Fit threshold despite an otherwise acceptable service-heavy model.</v>
+      </c>
+      <c r="U38" t="str">
+        <v>N</v>
+      </c>
+      <c r="V38" t="str">
+        <v>https://outlook.office365.com/owa/?ItemID=AAMkAGJiZDg3MTI0LWFhNzUtNGQzYS1hNWQzLWZlNDVmMmExMzRkNgBGAAAAAAD9u3VVtvqtSpWuAIjP80zoBwB5X058TjLSTIlO61qPMaSdAAAAAAEMAAB5X058TjLSTIlO61qPMaSdAAE98gknAAA%3D&amp;exvsurl=1&amp;viewmodel=ReadMessageItem</v>
+      </c>
+      <c r="W38" t="str">
+        <v>New</v>
+      </c>
+      <c r="X38" t="str">
+        <v>&lt;358b16f6-5aab-5a5b-91fa-3453fa0b87ee@pds.pdrserv.baystatebusinessbrokers.com&gt;</v>
+      </c>
+      <c r="Y38" t="str">
+        <v>2026-09-21T15:48:57Z</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y37"/>
+  <autoFilter ref="A1:Y38"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Y37"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y38"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/XIP_Deal_Funnel_Intake.xlsx
+++ b/data/XIP_Deal_Funnel_Intake.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Deal Funnel" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y39</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y38"/>
+  <dimension ref="A1:Y39"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -3355,10 +3355,87 @@
         <v>2026-09-21T15:48:57Z</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>DF-00038</v>
+      </c>
+      <c r="B39" t="str">
+        <v>2026-09-21T15:55:29Z</v>
+      </c>
+      <c r="C39" t="str">
+        <v>EARLY ACCESS: New Listing 1915, Award-Winning High-End Outdoor Lighting Business with $1.15M Annual Revenue</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Baystate Business Brokers &lt;admin@baystatebusinessbrokers.com&gt;</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Broker</v>
+      </c>
+      <c r="F39" t="str">
+        <v>Unknown (blind broker teaser — 'Listing 1915'; company name not disclosed in email)</v>
+      </c>
+      <c r="G39" t="str">
+        <v>Consumer-facing within mandate — residential/estate outdoor lighting design, installation &amp; service</v>
+      </c>
+      <c r="H39" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="I39" t="str">
+        <v>Unknown (only SDE stated, not EBITDA)</v>
+      </c>
+      <c r="J39" t="str">
+        <v>$1,102,337 (2025)</v>
+      </c>
+      <c r="K39" t="str">
+        <v>Unknown (SDE 2025 $131,696 on $1,102,337 revenue = ~12% SDE margin, not a true EBITDA margin)</v>
+      </c>
+      <c r="L39" t="str">
+        <v>$715,000 (Business Price)</v>
+      </c>
+      <c r="M39" t="str">
+        <v>Mixed — core installations 40-52% of sales ($5K-$75K+ projects), recurring service/tune-ups 18-25%, incremental upgrades 12-20%</v>
+      </c>
+      <c r="N39" t="str">
+        <v>Partial — semi-absentee ownership, General Manager runs daily operations, owner ~5-15 hrs/week strategic oversight; no CFO or ERP/systems mentioned</v>
+      </c>
+      <c r="O39" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="P39" t="str">
+        <v>BayState Business Brokers (John Brice)</v>
+      </c>
+      <c r="Q39" t="str">
+        <v>Duplicate broker blast of the same 'Listing 1915' campaign already logged as DF-00037 (~47 min earlier, different Message ID, identical content). 'Preferred Buyers' one-week early-access window; no NDA/CIM/attachment provided, teaser-level detail only. Diverse client base (hundreds of relationships, no concentration risk); demand exceeds current technician capacity.</v>
+      </c>
+      <c r="R39">
+        <v>33</v>
+      </c>
+      <c r="S39" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="T39" t="str">
+        <v>In-mandate but sub-scale residential outdoor-lighting design/install/service business with only ~$132K SDE and a $715K asking price, far below XIP's target EBITDA range, so it scores well under the Fit threshold; this is a repeat send of the same listing already logged as DF-00037.</v>
+      </c>
+      <c r="U39" t="str">
+        <v>N</v>
+      </c>
+      <c r="V39" t="str">
+        <v>https://outlook.office365.com/owa/?ItemID=AAMkAGJiZDg3MTI0LWFhNzUtNGQzYS1hNWQzLWZlNDVmMmExMzRkNgBGAAAAAAD9u3VVtvqtSpWuAIjP80zoBwB5X058TjLSTIlO61qPMaSdAAAAAAEMAAB5X058TjLSTIlO61qPMaSdAAE98gkoAAA%3D&amp;exvsurl=1&amp;viewmodel=ReadMessageItem</v>
+      </c>
+      <c r="W39" t="str">
+        <v>New</v>
+      </c>
+      <c r="X39" t="str">
+        <v>&lt;6f5dc0d0-0bdb-51d1-a385-9371e9c1fb2a@pds.pdrserv.baystatebusinessbrokers.com&gt;</v>
+      </c>
+      <c r="Y39" t="str">
+        <v>2026-09-21T16:49:29Z</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y38"/>
+  <autoFilter ref="A1:Y39"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Y38"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y39"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/XIP_Deal_Funnel_Intake.xlsx
+++ b/data/XIP_Deal_Funnel_Intake.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Deal Funnel" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y40</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y39"/>
+  <dimension ref="A1:Y40"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -3432,10 +3432,87 @@
         <v>2026-09-21T16:49:29Z</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>DF-00039</v>
+      </c>
+      <c r="B40" t="str">
+        <v>2026-09-21T21:02:23Z</v>
+      </c>
+      <c r="C40" t="str">
+        <v>EARLY ACCESS: New Listing 1930, Seasonal Waterfront Restaurant and Retail Market with Real Estate</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Baystate Business Brokers &lt;admin@baystatebusinessbrokers.com&gt;</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Broker</v>
+      </c>
+      <c r="F40" t="str">
+        <v>Unknown (blind broker teaser — 'Listing 1930'; company name not disclosed in email)</v>
+      </c>
+      <c r="G40" t="str">
+        <v>Consumer products/brands (seasonal waterfront seafood restaurant &amp; retail market)</v>
+      </c>
+      <c r="H40" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="I40" t="str">
+        <v>Unknown (only SDE stated, not EBITDA)</v>
+      </c>
+      <c r="J40" t="str">
+        <v>$4,343,141 (2025)</v>
+      </c>
+      <c r="K40" t="str">
+        <v>Unknown (SDE 2025 $880,193 on $4,343,141 revenue = ~20% SDE margin, not a true EBITDA margin)</v>
+      </c>
+      <c r="L40" t="str">
+        <v>$4,795,000 total ($2,965,000 business + $1,830,000 real estate; must be sold together)</v>
+      </c>
+      <c r="M40" t="str">
+        <v>Service/retail — seafood restaurant with retail seafood counter, takeout, online ordering, and off-site catering</v>
+      </c>
+      <c r="N40" t="str">
+        <v>Partial — email cites a 'seasoned leadership team' delivering consistent operations without adding payroll, but no CEO/CFO or ERP/systems detail given</v>
+      </c>
+      <c r="O40" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="P40" t="str">
+        <v>BayState Business Brokers (Bil Zarch)</v>
+      </c>
+      <c r="Q40" t="str">
+        <v>Broker 'Early Access' blast to Preferred Buyers, one-week early-access window; must be sold together with the real estate; no NDA/CIM/attachment provided, teaser-level detail only; hard-disqualified as consumer products/brand (restaurant/retail), out of XIP infra mandate.</v>
+      </c>
+      <c r="R40">
+        <v>0</v>
+      </c>
+      <c r="S40" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="T40" t="str">
+        <v>A seasonal waterfront seafood restaurant and retail market is a consumer products/hospitality business with no infrastructure-operating character, hard-disqualifying it under the mandate despite solid revenue and asking price.</v>
+      </c>
+      <c r="U40" t="str">
+        <v>N</v>
+      </c>
+      <c r="V40" t="str">
+        <v>https://outlook.office365.com/owa/?ItemID=AAMkAGJiZDg3MTI0LWFhNzUtNGQzYS1hNWQzLWZlNDVmMmExMzRkNgBGAAAAAAD9u3VVtvqtSpWuAIjP80zoBwB5X058TjLSTIlO61qPMaSdAAAAAAEXAAB5X058TjLSTIlO61qPMaSdAAE9tP40AAA%3D&amp;exvsurl=1&amp;viewmodel=ReadMessageItem</v>
+      </c>
+      <c r="W40" t="str">
+        <v>New</v>
+      </c>
+      <c r="X40" t="str">
+        <v>&lt;6c7e09d0-a439-5086-b8b4-900fbdde4b80@pds.pdrserv.baystatebusinessbrokers.com&gt;</v>
+      </c>
+      <c r="Y40" t="str">
+        <v>2026-09-21T21:49:21Z</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y39"/>
+  <autoFilter ref="A1:Y40"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Y39"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y40"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/XIP_Deal_Funnel_Intake.xlsx
+++ b/data/XIP_Deal_Funnel_Intake.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Deal Funnel" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y41</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y40"/>
+  <dimension ref="A1:Y41"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -3509,10 +3509,87 @@
         <v>2026-09-21T21:49:21Z</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>DF-00040</v>
+      </c>
+      <c r="B41" t="str">
+        <v>2026-09-25T16:03:47.000Z</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Deal Flow Friday: Active Sell-Side Engagements</v>
+      </c>
+      <c r="D41" t="str">
+        <v>dealflow@mariner.com</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Broker</v>
+      </c>
+      <c r="F41" t="str">
+        <v>Unknown (blind teaser: "Construction &amp; Engineering" business, CAD $11.1M EBITDA)</v>
+      </c>
+      <c r="G41" t="str">
+        <v>Energy Infrastructure Services</v>
+      </c>
+      <c r="H41" t="str">
+        <v>Unknown (EBITDA stated in CAD, suggesting Canada, but not explicitly stated)</v>
+      </c>
+      <c r="I41" t="str">
+        <v>CAD $11.1M</v>
+      </c>
+      <c r="J41" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="K41" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="L41" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="M41" t="str">
+        <v>Construction &amp; Engineering (capex-heavy)</v>
+      </c>
+      <c r="N41" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="O41" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="P41" t="str">
+        <v>Mariner (Woodbridge International LLC, a subsidiary of Mariner Wealth Advisors)</v>
+      </c>
+      <c r="Q41" t="str">
+        <v>Blind teaser (no company name) from Mariner's weekly "Deal Flow Friday" advertisement/marketing digest email; only an NDA link was provided, not accessed. Fourth logged appearance of this exact CAD $11.1M EBITDA / Energy Infrastructure Services line item, after DF-00021 (2026-08-14), DF-00024 (2026-08-21) and DF-00032 (2026-09-04); logged again since it carries a distinct messageId, so not auto-deduped. Email bundled 21 other one-line teasers this run (vertically integrated healthcare platform, museum/tradeshow exhibit platform, noise/flow/vibration/dispersion control products &amp; services, specialty building infrastructure &amp; compliance contractor, grooming products brand, military training &amp; logistics, waste management, offshore equipment rental, food safety/FDA compliance, industrial components manufacturer, environmental services contractor, real estate media, automotive parts manufacturer, cleaning/specialty chemical products, management consulting, environmental engineering &amp; remediation, IT/regulatory compliance consulting, staffing/talent solutions, trucking &amp; logistics, valve services, aircraft parts/MRO); all excluded consistent with prior runs as either out of mandate (consumer brand, professional/consulting services, manufacturing, staffing, media, defense/aerospace, automotive) or too generic/unconfirmed to confidently place as core infrastructure (building-compliance/environmental/valve/noise-control "services" teasers with no stated utility, grid, or infra-asset context). This was again the only line item with an explicit "Energy Infrastructure Services" sector tag.</v>
+      </c>
+      <c r="R41">
+        <v>67</v>
+      </c>
+      <c r="S41" t="str">
+        <v>Fit</v>
+      </c>
+      <c r="T41" t="str">
+        <v>Explicitly tagged "Energy Infrastructure Services" end-market (35/35) with mid-size EBITDA in the sweet-spot range (24/30, margin unstated) places it in the Fit tier, but it is a fully blind, unnamed, capex-heavy teaser repeating DF-00021/DF-00024/DF-00032 with no new detail, so treat as low-confidence until a company name and NDA-stage detail emerge.</v>
+      </c>
+      <c r="U41" t="str">
+        <v>N</v>
+      </c>
+      <c r="V41" t="str">
+        <v>https://outlook.office365.com/owa/?ItemID=AAMkAGJiZDg3MTI0LWFhNzUtNGQzYS1hNWQzLWZlNDVmMmExMzRkNgBGAAAAAAD9u3VVtvqtSpWuAIjP80zoBwB5X058TjLSTIlO61qPMaSdAAAAAAEMAAB5X058TjLSTIlO61qPMaSdAAFGM44lAAA%3D&amp;exvsurl=1&amp;viewmodel=ReadMessageItem</v>
+      </c>
+      <c r="W41" t="str">
+        <v>New</v>
+      </c>
+      <c r="X41" t="str">
+        <v>&lt;1142349142548.1142301062071.1067269665.0.1261200JL.2002@synd.ccsend.com&gt;</v>
+      </c>
+      <c r="Y41" t="str">
+        <v>2026-09-25T16:48:28Z</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y40"/>
+  <autoFilter ref="A1:Y41"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Y40"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y41"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/XIP_Deal_Funnel_Intake.xlsx
+++ b/data/XIP_Deal_Funnel_Intake.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Deal Funnel" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y42</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y41"/>
+  <dimension ref="A1:Y42"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -3586,10 +3586,87 @@
         <v>2026-09-25T16:48:28Z</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>DF-00041</v>
+      </c>
+      <c r="B42" t="str">
+        <v>2026-09-25T17:49:19Z</v>
+      </c>
+      <c r="C42" t="str">
+        <v>New Listing 1915:  Award-Winning, High-End Outdoor Lighting Business with $1.5M in Annual Revenue</v>
+      </c>
+      <c r="D42" t="str">
+        <v>admin@baystatebusinessbrokers.com</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Broker</v>
+      </c>
+      <c r="F42" t="str">
+        <v>Unknown (redacted broker listing, "Listing 1915" - high-end outdoor/architectural lighting design &amp; installation business)</v>
+      </c>
+      <c r="G42" t="str">
+        <v>Consumer-facing business within mandate (residential/estate exterior lighting design, installation &amp; electrical service for affluent homeowners)</v>
+      </c>
+      <c r="H42" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="I42" t="str">
+        <v>Unknown (SDE 2025: $131,969)</v>
+      </c>
+      <c r="J42" t="str">
+        <v>$1,102,337 (2025)</v>
+      </c>
+      <c r="K42" t="str">
+        <v>Unknown (SDE margin ~12%)</v>
+      </c>
+      <c r="L42" t="str">
+        <v>$715,000</v>
+      </c>
+      <c r="M42" t="str">
+        <v>Mixed (project-based installs 40-52% of sales; recurring seasonal service/repairs 18-25%; incremental upgrades/LED conversions 12-20%)</v>
+      </c>
+      <c r="N42" t="str">
+        <v>Partial (semi-absentee; General Manager runs daily ops, owner ~5-15 hrs/week strategic oversight; no ERP/systems mentioned)</v>
+      </c>
+      <c r="O42" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="P42" t="str">
+        <v>BayState Business Brokers</v>
+      </c>
+      <c r="Q42" t="str">
+        <v>NDA required for further info (signup link in email); broad diversified client base, no single-client concentration; well below XIP's target deal size (SDE ~$132K vs. $3-20M sweet spot).</v>
+      </c>
+      <c r="R42">
+        <v>35</v>
+      </c>
+      <c r="S42" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="T42" t="str">
+        <v>Small (~$132K SDE), owner/broker-listed residential lighting-install business is directionally in-mandate as a consumer-facing electrical/home-services company but is far too small for XIP's target check size and lacks scaled systems, landing well below the Fit threshold.</v>
+      </c>
+      <c r="U42" t="str">
+        <v>N</v>
+      </c>
+      <c r="V42" t="str">
+        <v>https://outlook.office365.com/owa/?ItemID=AAMkAGJiZDg3MTI0LWFhNzUtNGQzYS1hNWQzLWZlNDVmMmExMzRkNgBGAAAAAAD9u3VVtvqtSpWuAIjP80zoBwB5X058TjLSTIlO61qPMaSdAAAAAAEMAAB5X058TjLSTIlO61qPMaSdAAFGM44mAAA%3D&amp;exvsurl=1&amp;viewmodel=ReadMessageItem</v>
+      </c>
+      <c r="W42" t="str">
+        <v>New</v>
+      </c>
+      <c r="X42" t="str">
+        <v>&lt;6d099f20-ff9d-5a10-8ec6-afbaf52fb2d4@pds.pdrserv.baystatebusinessbrokers.com&gt;</v>
+      </c>
+      <c r="Y42" t="str">
+        <v>2026-09-25T17:49:21Z</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y41"/>
+  <autoFilter ref="A1:Y42"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Y41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y42"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/XIP_Deal_Funnel_Intake.xlsx
+++ b/data/XIP_Deal_Funnel_Intake.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Deal Funnel" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y43</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y42"/>
+  <dimension ref="A1:Y43"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -3663,10 +3663,87 @@
         <v>2026-09-25T17:49:21Z</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>DF-00042</v>
+      </c>
+      <c r="B43" t="str">
+        <v>2026-09-29T15:17:35Z</v>
+      </c>
+      <c r="C43" t="str">
+        <v>New Listing 1915: Seasonal Waterfront Restaurant &amp; Retail Market with Real Estate In MA</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Baystate Business Brokers &lt;admin@baystatebusinessbrokers.com&gt;</v>
+      </c>
+      <c r="E43" t="str">
+        <v>Broker</v>
+      </c>
+      <c r="F43" t="str">
+        <v>Unknown (blind broker teaser — "Listing 1930" per body banner, though subject line says "Listing 1915"; company name not disclosed in email)</v>
+      </c>
+      <c r="G43" t="str">
+        <v>Consumer products/brands (seasonal waterfront seafood restaurant &amp; retail market)</v>
+      </c>
+      <c r="H43" t="str">
+        <v>Massachusetts (per subject line "In MA"; not detailed further in email)</v>
+      </c>
+      <c r="I43" t="str">
+        <v>Unknown (only SDE stated, not EBITDA)</v>
+      </c>
+      <c r="J43" t="str">
+        <v>$4,343,141 (2025)</v>
+      </c>
+      <c r="K43" t="str">
+        <v>Unknown (SDE 2025 $880,193 on $4,343,141 revenue = ~20% SDE margin, not a true EBITDA margin)</v>
+      </c>
+      <c r="L43" t="str">
+        <v>$4,795,000 total ($2,965,000 business + $1,830,000 real estate; must be sold together)</v>
+      </c>
+      <c r="M43" t="str">
+        <v>Service/retail — seafood restaurant with retail seafood counter, takeout, online ordering, and off-site catering</v>
+      </c>
+      <c r="N43" t="str">
+        <v>Partial — email cites a "seasoned leadership team" delivering consistent operations without adding payroll, but no CEO/CFO or ERP/systems detail given</v>
+      </c>
+      <c r="O43" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="P43" t="str">
+        <v>BayState Business Brokers (Bil Zarch)</v>
+      </c>
+      <c r="Q43" t="str">
+        <v>Repeat broker blast of the same "Listing 1930" seafood restaurant/retail-market content already logged as DF-00039 (2026-09-21), now resent under a mismatched "Listing 1915" subject line with an explicit "In MA" geography tag; NDA required via e-sign link, no CIM/attachment provided; hard-disqualified as consumer products/brand (restaurant/retail), out of XIP infra mandate.</v>
+      </c>
+      <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="T43" t="str">
+        <v>A seasonal waterfront seafood restaurant and retail market is a consumer products/hospitality business with no infrastructure-operating character, hard-disqualifying it under the mandate despite solid revenue and asking price; this is a repeat send of the same listing already logged as DF-00039.</v>
+      </c>
+      <c r="U43" t="str">
+        <v>N</v>
+      </c>
+      <c r="V43" t="str">
+        <v>https://outlook.office365.com/owa/?ItemID=AAMkAGJiZDg3MTI0LWFhNzUtNGQzYS1hNWQzLWZlNDVmMmExMzRkNgBGAAAAAAD9u3VVtvqtSpWuAIjP80zoBwB5X058TjLSTIlO61qPMaSdAAAAAAEMAAB5X058TjLSTIlO61qPMaSdAAFP5PO9AAA%3D&amp;exvsurl=1&amp;viewmodel=ReadMessageItem</v>
+      </c>
+      <c r="W43" t="str">
+        <v>New</v>
+      </c>
+      <c r="X43" t="str">
+        <v>&lt;9e1320a4-6972-5806-afa4-e226a6e8784a@pds.pdrserv.baystatebusinessbrokers.com&gt;</v>
+      </c>
+      <c r="Y43" t="str">
+        <v>2026-09-29T15:50:15Z</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y42"/>
+  <autoFilter ref="A1:Y43"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Y42"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y43"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/XIP_Deal_Funnel_Intake.xlsx
+++ b/data/XIP_Deal_Funnel_Intake.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Deal Funnel" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y44</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y43"/>
+  <dimension ref="A1:Y44"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -3740,10 +3740,87 @@
         <v>2026-09-29T15:50:15Z</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>DF-00043</v>
+      </c>
+      <c r="B44" t="str">
+        <v>2026-09-29T19:45:48Z</v>
+      </c>
+      <c r="C44" t="str">
+        <v>EARLY ACCESS: New Listing 1933, Two Established Massage &amp; Wellness Centers | Strong Membership Revenue &amp; Growth Potential</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Baystate Business Brokers &lt;admin@baystatebusinessbrokers.com&gt;</v>
+      </c>
+      <c r="E44" t="str">
+        <v>Broker</v>
+      </c>
+      <c r="F44" t="str">
+        <v>Unknown (blind broker teaser — subject says "Listing 1933" but body banner says "Listing 1934"; company name not disclosed, operates under a nationally recognized wellness franchise brand with 290+ studios nationwide)</v>
+      </c>
+      <c r="G44" t="str">
+        <v>Consumer products/brands (membership-based massage &amp; wellness studio franchise)</v>
+      </c>
+      <c r="H44" t="str">
+        <v>Massachusetts (both studios operate in MA markets; specific cities not stated)</v>
+      </c>
+      <c r="I44" t="str">
+        <v>Unknown (only SDE stated, not EBITDA)</v>
+      </c>
+      <c r="J44" t="str">
+        <v>$2,518,623 combined 2025 (Location 1: $1,259,280; Location 2: $1,259,343)</v>
+      </c>
+      <c r="K44" t="str">
+        <v>Unknown (combined SDE 2025 $310,295 on $2,518,623 revenue = ~12% SDE margin, not a true EBITDA margin)</v>
+      </c>
+      <c r="L44" t="str">
+        <v>$948,000 total ($549,000 Location 1 + $399,000 Location 2)</v>
+      </c>
+      <c r="M44" t="str">
+        <v>Service — membership-based massage, wellness, and spa services (Swedish/deep-tissue/hot-stone massage, stretch sessions, facials) with ~80-85% recurring monthly membership revenue plus retail product sales</v>
+      </c>
+      <c r="N44" t="str">
+        <v>Partial — combined 51-person trained staff expected to remain through transition; no CEO/CFO or ERP/systems detail given</v>
+      </c>
+      <c r="O44" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="P44" t="str">
+        <v>BayState Business Brokers (John Brice)</v>
+      </c>
+      <c r="Q44" t="str">
+        <v>Broker 'Early Access' blast to Preferred Buyers, one-week early-access window; subject line says 'Listing 1933' but body banner says 'Listing 1934' (listing-number mismatch, similar to prior DF-00042 mismatch); operates under a nationally recognized wellness franchise brand with 290+ studios nationwide; both studios recently renovated to brand standards, leases secured through 2030/2032, 1,643 combined active paying members (22% growth at Location 1 since 2023, stable 764-member base at Location 2); no NDA/CIM/attachment provided, teaser-level detail only; hard-disqualified as consumer products/brand (personal-care/wellness franchise), out of XIP infra mandate.</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="T44" t="str">
+        <v>A membership-based massage and wellness studio franchise is a consumer products/personal-care business with no infrastructure-operating character, hard-disqualifying it under the mandate despite strong recurring membership revenue and secured long-term leases.</v>
+      </c>
+      <c r="U44" t="str">
+        <v>N</v>
+      </c>
+      <c r="V44" t="str">
+        <v>https://outlook.office365.com/owa/?ItemID=AAMkAGJiZDg3MTI0LWFhNzUtNGQzYS1hNWQzLWZlNDVmMmExMzRkNgBGAAAAAAD9u3VVtvqtSpWuAIjP80zoBwB5X058TjLSTIlO61qPMaSdAAAAAAEMAAB5X058TjLSTIlO61qPMaSdAAFP5PO%2FAAA%3D&amp;exvsurl=1&amp;viewmodel=ReadMessageItem</v>
+      </c>
+      <c r="W44" t="str">
+        <v>New</v>
+      </c>
+      <c r="X44" t="str">
+        <v>&lt;60be880c-fdb1-5ef2-8cfa-b8d07d1a3a57@pds.pdrserv.baystatebusinessbrokers.com&gt;</v>
+      </c>
+      <c r="Y44" t="str">
+        <v>2026-09-29T19:50:50Z</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y43"/>
+  <autoFilter ref="A1:Y44"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Y43"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y44"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/XIP_Deal_Funnel_Intake.xlsx
+++ b/data/XIP_Deal_Funnel_Intake.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Deal Funnel" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y45</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y44"/>
+  <dimension ref="A1:Y45"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -3817,10 +3817,87 @@
         <v>2026-09-29T19:50:50Z</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>DF-00044</v>
+      </c>
+      <c r="B45" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C45" t="str">
+        <v>EARLY ACCESS: New Listing 1934, Institutional Construction Manager | Greater Boston, MA</v>
+      </c>
+      <c r="D45" t="str">
+        <v>admin@baystatebusinessbrokers.com</v>
+      </c>
+      <c r="E45" t="str">
+        <v>Broker</v>
+      </c>
+      <c r="F45" t="str">
+        <v>40-Year Academic Contractor (Listing 1934)</v>
+      </c>
+      <c r="G45" t="str">
+        <v>Institutional Construction (Non-Infra)</v>
+      </c>
+      <c r="H45" t="str">
+        <v>Greater Boston, MA</v>
+      </c>
+      <c r="I45" t="str">
+        <v>SDE $1,023,194 (3-yr avg); EBITDA not stated</v>
+      </c>
+      <c r="J45" t="str">
+        <v>$6,759,078 (3-yr avg)</v>
+      </c>
+      <c r="K45" t="str">
+        <v>~15% (SDE basis)</v>
+      </c>
+      <c r="L45" t="str">
+        <v>$3,900,000</v>
+      </c>
+      <c r="M45" t="str">
+        <v>Capex-Heavy Construction</v>
+      </c>
+      <c r="N45" t="str">
+        <v>Founder-only / Unknown (no stated systems)</v>
+      </c>
+      <c r="O45" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="P45" t="str">
+        <v>Baystate Business Brokers</v>
+      </c>
+      <c r="Q45" t="str">
+        <v>Marketed as one-week 'Early Access' for Preferred Buyers; no NDA/CIM status stated</v>
+      </c>
+      <c r="R45">
+        <v>22</v>
+      </c>
+      <c r="S45" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="T45" t="str">
+        <v>General institutional renovation/maintenance contractor for academic clients around Boston -- not an infra asset-operator (no energy/telecom/water/transportation exposure) and not residential-consumer either, so End-Market scores low; sub-$3M SDE (EBITDA unstated), capex-heavy project mix, no stated management systems, and sourced via a generic broker blast keep the total well into Pass territory.</v>
+      </c>
+      <c r="U45" t="str">
+        <v>N</v>
+      </c>
+      <c r="V45" t="str">
+        <v>https://outlook.office365.com/owa/?ItemID=AAMkAGJiZDg3MTI0LWFhNzUtNGQzYS1hNWQzLWZlNDVmMmExMzRkNgBGAAAAAAD9u3VVtvqtSpWuAIjP80zoBwB5X058TjLSTIlO61qPMaSdAAAAAAEMAAB5X058TjLSTIlO61qPMaSdAAFP5PPAAAA%3D&amp;exvsurl=1&amp;viewmodel=ReadMessageItem</v>
+      </c>
+      <c r="W45" t="str">
+        <v>New</v>
+      </c>
+      <c r="X45" t="str">
+        <v>&lt;a14ff417-1525-572c-9580-3319f1b3618a@pds.pdrserv.baystatebusinessbrokers.com&gt;</v>
+      </c>
+      <c r="Y45" t="str">
+        <v>2026-10-01T15:50:25Z</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y44"/>
+  <autoFilter ref="A1:Y45"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Y44"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y45"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/XIP_Deal_Funnel_Intake.xlsx
+++ b/data/XIP_Deal_Funnel_Intake.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Deal Funnel" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y46</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y45"/>
+  <dimension ref="A1:Y46"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -3894,10 +3894,87 @@
         <v>2026-10-01T15:50:25Z</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>DF-00045</v>
+      </c>
+      <c r="B46" t="str">
+        <v>2026-10-01T18:45:22Z</v>
+      </c>
+      <c r="C46" t="str">
+        <v>EARLY ACCESS: New Listing 1937, Absentee Owned, Premium Tile &amp; Surface Retailer for High Ticket Renovations in Southwest Connecticut</v>
+      </c>
+      <c r="D46" t="str">
+        <v>admin@baystatebusinessbrokers.com</v>
+      </c>
+      <c r="E46" t="str">
+        <v>Broker</v>
+      </c>
+      <c r="F46" t="str">
+        <v>Unknown (Listing 1937 - anonymized)</v>
+      </c>
+      <c r="G46" t="str">
+        <v>Specialty retail / building materials distribution (tile, stone, bath products) - consumer retail, not infrastructure</v>
+      </c>
+      <c r="H46" t="str">
+        <v>Southwest Connecticut</v>
+      </c>
+      <c r="I46" t="str">
+        <v>$443,000 (Adj. EBITDA 2025)</v>
+      </c>
+      <c r="J46" t="str">
+        <v>$3,763,000 (2025)</v>
+      </c>
+      <c r="K46" t="str">
+        <v>~11.8%</v>
+      </c>
+      <c r="L46" t="str">
+        <v>$1,850,000 + Inventory</v>
+      </c>
+      <c r="M46" t="str">
+        <v>Mixed (specialty retail showroom + trade/contractor distribution)</v>
+      </c>
+      <c r="N46" t="str">
+        <v>Partial - absentee owner, long-tenured team (15+ yrs key employees) runs daily operations and expected to stay post-sale; no ERP/systems mentioned</v>
+      </c>
+      <c r="O46" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="P46" t="str">
+        <v>BayState Business Brokers</v>
+      </c>
+      <c r="Q46" t="str">
+        <v>Early-access listing open to 'Preferred Buyers' for one week; no NDA/CIM mention yet; absentee owner, management team expected to remain after sale.</v>
+      </c>
+      <c r="R46">
+        <v>25</v>
+      </c>
+      <c r="S46" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="T46" t="str">
+        <v>Absentee-owned specialty tile/stone/bath retailer serving designers, contractors and homeowners in Southwest CT - a consumer retail/distribution business with no infrastructure-operating character, so it is hard-disqualified as out of mandate despite a manageable price and solid ~12% EBITDA margin.</v>
+      </c>
+      <c r="U46" t="str">
+        <v>N</v>
+      </c>
+      <c r="V46" t="str">
+        <v>https://outlook.office365.com/owa/?ItemID=AAMkAGJiZDg3MTI0LWFhNzUtNGQzYS1hNWQzLWZlNDVmMmExMzRkNgBGAAAAAAD9u3VVtvqtSpWuAIjP80zoBwB5X058TjLSTIlO61qPMaSdAAAAAAEMAAB5X058TjLSTIlO61qPMaSdAAFP5PPBAAA%3D&amp;exvsurl=1&amp;viewmodel=ReadMessageItem</v>
+      </c>
+      <c r="W46" t="str">
+        <v>New</v>
+      </c>
+      <c r="X46" t="str">
+        <v>&lt;91530cb9-52b1-5ac0-996c-531e74452027@pds.pdrserv.baystatebusinessbrokers.com&gt;</v>
+      </c>
+      <c r="Y46" t="str">
+        <v>2026-10-01T18:49:17Z</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y45"/>
+  <autoFilter ref="A1:Y46"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Y45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y46"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/XIP_Deal_Funnel_Intake.xlsx
+++ b/data/XIP_Deal_Funnel_Intake.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Deal Funnel" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y47</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y46"/>
+  <dimension ref="A1:Y47"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -3971,10 +3971,87 @@
         <v>2026-10-01T18:49:17Z</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>DF-00046</v>
+      </c>
+      <c r="B47" t="str">
+        <v>2026-10-02T14:26:32Z</v>
+      </c>
+      <c r="C47" t="str">
+        <v>New Listing 1929, Established Multi-Store Ice Cream Business | Proven Growth</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Baystate Business Brokers &lt;admin@baystatebusinessbrokers.com&gt;</v>
+      </c>
+      <c r="E47" t="str">
+        <v>Broker</v>
+      </c>
+      <c r="F47" t="str">
+        <v>Unknown (blind broker teaser - "Listing 1929"; company name not disclosed)</v>
+      </c>
+      <c r="G47" t="str">
+        <v>Consumer products/brands (multi-store ice cream retailer/dessert shop chain)</v>
+      </c>
+      <c r="H47" t="str">
+        <v>Greater Boston, Massachusetts</v>
+      </c>
+      <c r="I47" t="str">
+        <v>Unknown (only SDE stated, not EBITDA)</v>
+      </c>
+      <c r="J47" t="str">
+        <v>$3,797,749 (2025)</v>
+      </c>
+      <c r="K47" t="str">
+        <v>Unknown (SDE 2025 $426,120 on $3,797,749 revenue = ~11.2% SDE margin, not a true EBITDA margin)</v>
+      </c>
+      <c r="L47" t="str">
+        <v>$1,495,000 (Business Price)</v>
+      </c>
+      <c r="M47" t="str">
+        <v>Retail/service - multi-store ice cream &amp; frozen dessert retailer (scooped desserts, take-home pints/quarts/half-gallons, cakes); seasonal peak May-Aug</v>
+      </c>
+      <c r="N47" t="str">
+        <v>Partial - manager-run stores with no regular founder store-duty involvement; operations continued well during an extended founder absence; no CEO/CFO or ERP/systems detail given</v>
+      </c>
+      <c r="O47" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="P47" t="str">
+        <v>BayState Business Brokers (Bil Zarch)</v>
+      </c>
+      <c r="Q47" t="str">
+        <v>'New Listing' broker blast email; NDA e-sign link required for more information, no CIM/attachment provided; hard-disqualified as consumer products/brand (retail ice cream chain), out of XIP infra mandate.</v>
+      </c>
+      <c r="R47">
+        <v>0</v>
+      </c>
+      <c r="S47" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="T47" t="str">
+        <v>A multi-store Greater Boston ice cream retailer is a consumer products/food-retail business with no infrastructure-operating character, hard-disqualifying it under the mandate despite steady seasonal revenue and a modest asking price.</v>
+      </c>
+      <c r="U47" t="str">
+        <v>N</v>
+      </c>
+      <c r="V47" t="str">
+        <v>https://outlook.office365.com/owa/?ItemID=AAMkAGJiZDg3MTI0LWFhNzUtNGQzYS1hNWQzLWZlNDVmMmExMzRkNgBGAAAAAAD9u3VVtvqtSpWuAIjP80zoBwB5X058TjLSTIlO61qPMaSdAAAAAAEMAAB5X058TjLSTIlO61qPMaSdAAFT%2FMQvAAA%3D&amp;exvsurl=1&amp;viewmodel=ReadMessageItem</v>
+      </c>
+      <c r="W47" t="str">
+        <v>New</v>
+      </c>
+      <c r="X47" t="str">
+        <v>&lt;feee2797-83d2-5d58-863c-4f68b8c6ff6e@pds.pdrserv.baystatebusinessbrokers.com&gt;</v>
+      </c>
+      <c r="Y47" t="str">
+        <v>2026-10-02T14:52:00Z</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y46"/>
+  <autoFilter ref="A1:Y47"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Y46"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y47"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/XIP_Deal_Funnel_Intake.xlsx
+++ b/data/XIP_Deal_Funnel_Intake.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Deal Funnel" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y48</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y47"/>
+  <dimension ref="A1:Y48"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -4048,10 +4048,87 @@
         <v>2026-10-02T14:52:00Z</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>DF-00047</v>
+      </c>
+      <c r="B48" t="str">
+        <v>2026-10-02T18:23:32Z</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Listing: 1894, Fully Integrated Behavioral Health Practice with Experienced Client Team</v>
+      </c>
+      <c r="D48" t="str">
+        <v>admin@baystatebusinessbrokers.com</v>
+      </c>
+      <c r="E48" t="str">
+        <v>Broker</v>
+      </c>
+      <c r="F48" t="str">
+        <v>Listing 1894 (unnamed outpatient behavioral health practice)</v>
+      </c>
+      <c r="G48" t="str">
+        <v>Outpatient behavioral health / medical practice (not infra, not infra-adjacent residential service)</v>
+      </c>
+      <c r="H48" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="I48" t="str">
+        <v>$513,000 (3-year average)</v>
+      </c>
+      <c r="J48" t="str">
+        <v>$2,883,195 (3-year average)</v>
+      </c>
+      <c r="K48" t="str">
+        <v>~17.8%</v>
+      </c>
+      <c r="L48" t="str">
+        <v>$1,650,000 (business price)</v>
+      </c>
+      <c r="M48" t="str">
+        <v>Service-oriented outpatient clinical practice (psychiatric medication management, therapy, TMS); not capex-heavy</v>
+      </c>
+      <c r="N48" t="str">
+        <v>Provider-dense clinical staff plus dedicated internal billing/insurance/collections/finance teams and EMR/practice-management systems (UnifiMD, LYTEC, RingCentral); no professional CEO/CFO mentioned</v>
+      </c>
+      <c r="O48" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="P48" t="str">
+        <v>BayState Business Brokers</v>
+      </c>
+      <c r="Q48" t="str">
+        <v>NDA required via click-to-sign link before further info; broker contact Stephanie Bloch</v>
+      </c>
+      <c r="R48">
+        <v>34</v>
+      </c>
+      <c r="S48" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="T48" t="str">
+        <v>Outpatient psychiatric/behavioral health practice is outside XIP's infrastructure and infra-adjacent-residential-service mandate, and EBITDA ($513K) is well below the target range, so despite a decent service-business model and real operating systems this scores Pass.</v>
+      </c>
+      <c r="U48" t="str">
+        <v>N</v>
+      </c>
+      <c r="V48" t="str">
+        <v>https://outlook.office365.com/owa/?ItemID=AAMkAGJiZDg3MTI0LWFhNzUtNGQzYS1hNWQzLWZlNDVmMmExMzRkNgBGAAAAAAD9u3VVtvqtSpWuAIjP80zoBwB5X058TjLSTIlO61qPMaSdAAAAAAEMAAB5X058TjLSTIlO61qPMaSdAAFT%2FMQxAAA%3D&amp;exvsurl=1&amp;viewmodel=ReadMessageItem</v>
+      </c>
+      <c r="W48" t="str">
+        <v>New</v>
+      </c>
+      <c r="X48" t="str">
+        <v>&lt;7c21ee2d-f2b2-5939-a22c-414e46aef0fb@pds.pdrserv.baystatebusinessbrokers.com&gt;</v>
+      </c>
+      <c r="Y48" t="str">
+        <v>2026-10-02T18:49:07Z</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y47"/>
+  <autoFilter ref="A1:Y48"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Y47"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y48"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/XIP_Deal_Funnel_Intake.xlsx
+++ b/data/XIP_Deal_Funnel_Intake.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Deal Funnel" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y49</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y48"/>
+  <dimension ref="A1:Y49"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -4125,10 +4125,87 @@
         <v>2026-10-02T18:49:07Z</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>DF-00048</v>
+      </c>
+      <c r="B49" t="str">
+        <v>2026-10-05T15:12:37Z</v>
+      </c>
+      <c r="C49" t="str">
+        <v>New Listing 1933: Two-Location Massage and Wellness Business with Loyal Membership Base</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Baystate Business Brokers &lt;admin@baystatebusinessbrokers.com&gt;</v>
+      </c>
+      <c r="E49" t="str">
+        <v>Broker</v>
+      </c>
+      <c r="F49" t="str">
+        <v>Unknown (blind broker listing - "Listing 1933"; franchise/company name not disclosed)</v>
+      </c>
+      <c r="G49" t="str">
+        <v>Consumer products/brands (membership-based massage &amp; wellness franchise studios, personal-care retail service, not infrastructure)</v>
+      </c>
+      <c r="H49" t="str">
+        <v>Massachusetts</v>
+      </c>
+      <c r="I49" t="str">
+        <v>Unknown (only TTM SDE stated, not EBITDA: $175,885 + $134,410 = $310,295 combined)</v>
+      </c>
+      <c r="J49" t="str">
+        <v>$2,518,623 (combined 2025: $1,259,280 + $1,259,343)</v>
+      </c>
+      <c r="K49" t="str">
+        <v>Unknown (SDE basis only; combined SDE $310,295 / combined revenue $2,518,623 = ~12.3% SDE margin, not a true EBITDA margin)</v>
+      </c>
+      <c r="L49" t="str">
+        <v>$948,000 total (Location 1 $549,000 + Location 2 $399,000)</v>
+      </c>
+      <c r="M49" t="str">
+        <v>Service-oriented membership-based massage, stretch, and facial services under a national wellness franchise brand (recurring auto-billed memberships drive ~80-85% of revenue); not capex-heavy - both studios recently renovated to brand standard</v>
+      </c>
+      <c r="N49" t="str">
+        <v>Partial - combined 51-person trained staff expected to remain through transition; no professional CEO/CFO or ERP/systems detail given</v>
+      </c>
+      <c r="O49" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="P49" t="str">
+        <v>BayState Business Brokers (John Brice)</v>
+      </c>
+      <c r="Q49" t="str">
+        <v>Click-to-sign NDA required for more info; no CIM/attachment provided; two studios offered together as a combined portfolio; leases secured through 2030 and 2032 support SBA/conventional financing</v>
+      </c>
+      <c r="R49">
+        <v>34</v>
+      </c>
+      <c r="S49" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="T49" t="str">
+        <v>A two-location membership-based massage and wellness franchise is a consumer personal-care/retail service business with no infrastructure-operating character, hard-disqualifying it under XIP's mandate despite a modest ~$948K combined asking price and recurring membership revenue.</v>
+      </c>
+      <c r="U49" t="str">
+        <v>N</v>
+      </c>
+      <c r="V49" t="str">
+        <v>https://outlook.office365.com/owa/?ItemID=AAMkAGJiZDg3MTI0LWFhNzUtNGQzYS1hNWQzLWZlNDVmMmExMzRkNgBGAAAAAAD9u3VVtvqtSpWuAIjP80zoBwB5X058TjLSTIlO61qPMaSdAAAAAAEMAAB5X058TjLSTIlO61qPMaSdAAFZP1MuAAA%3D&amp;exvsurl=1&amp;viewmodel=ReadMessageItem</v>
+      </c>
+      <c r="W49" t="str">
+        <v>New</v>
+      </c>
+      <c r="X49" t="str">
+        <v>&lt;3448cc0d-3ae5-5f74-8fa9-b48e9cf56c97@pds.pdrserv.baystatebusinessbrokers.com&gt;</v>
+      </c>
+      <c r="Y49" t="str">
+        <v>2026-10-05T15:50:12Z</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y48"/>
+  <autoFilter ref="A1:Y49"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Y48"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y49"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/XIP_Deal_Funnel_Intake.xlsx
+++ b/data/XIP_Deal_Funnel_Intake.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Deal Funnel" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y50</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y49"/>
+  <dimension ref="A1:Y50"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -4202,10 +4202,87 @@
         <v>2026-10-05T15:50:12Z</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>DF-00049</v>
+      </c>
+      <c r="B50" t="str">
+        <v>2026-10-07T12:39:52Z</v>
+      </c>
+      <c r="C50" t="str">
+        <v>New Listing 1934: 40-Year Academic Contractor with Recurring, Non-Binding Revenue</v>
+      </c>
+      <c r="D50" t="str">
+        <v>admin@baystatebusinessbrokers.com</v>
+      </c>
+      <c r="E50" t="str">
+        <v>Broker</v>
+      </c>
+      <c r="F50" t="str">
+        <v>40-Year Academic Contractor (Listing 1934, unnamed)</v>
+      </c>
+      <c r="G50" t="str">
+        <v>Other infra (institutional facilities renovation/maintenance contractor)</v>
+      </c>
+      <c r="H50" t="str">
+        <v>Greater Boston</v>
+      </c>
+      <c r="I50" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="J50" t="str">
+        <v>$6,759,078 (3-yr avg)</v>
+      </c>
+      <c r="K50" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="L50" t="str">
+        <v>$3,900,000 (Business Price)</v>
+      </c>
+      <c r="M50" t="str">
+        <v>Mixed (mostly project-based institutional renovation/millwork; some recurring maintenance via 3 dedicated carpenters)</v>
+      </c>
+      <c r="N50" t="str">
+        <v>Unknown (no mention of professional CEO/CFO or ERP systems; 15-person team since 1986)</v>
+      </c>
+      <c r="O50" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="P50" t="str">
+        <v>BayState Business Brokers</v>
+      </c>
+      <c r="Q50" t="str">
+        <v>NDA required via link to view further details/CIM; SDE 3-yr avg $1,023,194 stated (not EBITDA, so EBITDA marked Unknown); no attachments.</v>
+      </c>
+      <c r="R50">
+        <v>36</v>
+      </c>
+      <c r="S50" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="T50" t="str">
+        <v>Institutional building renovation/maintenance/millwork contractor serving academic clients in Greater Boston — a capex-heavy specialty contractor, not an infra asset-operator, with sub-$3M implied EBITDA (SDE only $1.02M on $6.76M revenue) putting it well below the financial sweet spot.</v>
+      </c>
+      <c r="U50" t="str">
+        <v>N</v>
+      </c>
+      <c r="V50" t="str">
+        <v>https://outlook.office365.com/owa/?ItemID=AAMkAGJiZDg3MTI0LWFhNzUtNGQzYS1hNWQzLWZlNDVmMmExMzRkNgBGAAAAAAD9u3VVtvqtSpWuAIjP80zoBwB5X058TjLSTIlO61qPMaSdAAAAAAEMAAB5X058TjLSTIlO61qPMaSdAAFdXfl4AAA%3D&amp;exvsurl=1&amp;viewmodel=ReadMessageItem</v>
+      </c>
+      <c r="W50" t="str">
+        <v>New</v>
+      </c>
+      <c r="X50" t="str">
+        <v>&lt;8955678e-3318-5dc0-bd61-ff112fb8ebc8@pds.pdrserv.baystatebusinessbrokers.com&gt;</v>
+      </c>
+      <c r="Y50" t="str">
+        <v>2026-10-07T12:48:58Z</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y49"/>
+  <autoFilter ref="A1:Y50"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Y49"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y50"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/XIP_Deal_Funnel_Intake.xlsx
+++ b/data/XIP_Deal_Funnel_Intake.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Deal Funnel" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y51</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y50"/>
+  <dimension ref="A1:Y51"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -4279,10 +4279,87 @@
         <v>2026-10-07T12:48:58Z</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>DF-00050</v>
+      </c>
+      <c r="B51" t="str">
+        <v>2026-10-07T18:06:21Z</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Listing: 1909, Turn-Key Boston Metro Behavioral Health Practice Offering Hybrid Care with Mostly-Absentee Owner</v>
+      </c>
+      <c r="D51" t="str">
+        <v>admin@baystatebusinessbrokers.com</v>
+      </c>
+      <c r="E51" t="str">
+        <v>Broker</v>
+      </c>
+      <c r="F51" t="str">
+        <v>Listing 1909 (unnamed Boston Metro behavioral health practice)</v>
+      </c>
+      <c r="G51" t="str">
+        <v>Outpatient behavioral health / group therapy practice (not infra, not infra-adjacent residential service)</v>
+      </c>
+      <c r="H51" t="str">
+        <v>Boston Metro, MA (Unknown further detail)</v>
+      </c>
+      <c r="I51" t="str">
+        <v>$250,871 (Adj. EBITDA, 2025)</v>
+      </c>
+      <c r="J51" t="str">
+        <v>$1,800,970 (2025)</v>
+      </c>
+      <c r="K51" t="str">
+        <v>~13.9%</v>
+      </c>
+      <c r="L51" t="str">
+        <v>$975,000 (business price)</v>
+      </c>
+      <c r="M51" t="str">
+        <v>Service-oriented outpatient group therapy practice (individual/couples/family therapy, specialized trauma/ADHD/mood-disorder care, group therapy); not capex-heavy</v>
+      </c>
+      <c r="N51" t="str">
+        <v>Employed clinicians generate 100% of revenue with owner spending only 5-10 hours/week (low founder-dependency); multi-office infrastructure can support 10 additional clinicians; no professional CEO/CFO or ERP system mentioned</v>
+      </c>
+      <c r="O51" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="P51" t="str">
+        <v>BayState Business Brokers</v>
+      </c>
+      <c r="Q51" t="str">
+        <v>NDA required via click-to-sign link before further info; broker contact Molly Hanson; mostly-absentee owner; &gt;14,000 annual sessions across office-based and statewide telehealth delivery</v>
+      </c>
+      <c r="R51">
+        <v>34</v>
+      </c>
+      <c r="S51" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="T51" t="str">
+        <v>Outpatient behavioral health/group therapy practice is outside XIP's infrastructure and infra-adjacent-residential-service mandate, and EBITDA ($251K) is well below the target range, so despite a low-founder-dependency service model with real scalable capacity this scores Pass.</v>
+      </c>
+      <c r="U51" t="str">
+        <v>N</v>
+      </c>
+      <c r="V51" t="str">
+        <v>https://outlook.office365.com/owa/?ItemID=AAMkAGJiZDg3MTI0LWFhNzUtNGQzYS1hNWQzLWZlNDVmMmExMzRkNgBGAAAAAAD9u3VVtvqtSpWuAIjP80zoBwB5X058TjLSTIlO61qPMaSdAAAAAAEMAAB5X058TjLSTIlO61qPMaSdAAFdXfl5AAA%3D&amp;exvsurl=1&amp;viewmodel=ReadMessageItem</v>
+      </c>
+      <c r="W51" t="str">
+        <v>New</v>
+      </c>
+      <c r="X51" t="str">
+        <v>&lt;74ff3536-4da7-5975-a078-18c01c28a408@pds.pdrserv.baystatebusinessbrokers.com&gt;</v>
+      </c>
+      <c r="Y51" t="str">
+        <v>2026-10-07T18:49:25Z</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y50"/>
+  <autoFilter ref="A1:Y51"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Y50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y51"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/XIP_Deal_Funnel_Intake.xlsx
+++ b/data/XIP_Deal_Funnel_Intake.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Deal Funnel" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y52</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y51"/>
+  <dimension ref="A1:Y52"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -4356,10 +4356,87 @@
         <v>2026-10-07T18:49:25Z</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>DF-00051</v>
+      </c>
+      <c r="B52" t="str">
+        <v>2026-10-12T20:39:23Z</v>
+      </c>
+      <c r="C52" t="str">
+        <v>EARLY ACCESS: New Listing 1925, Geotechnical Drilling &amp; Specialty Foundation Contractor</v>
+      </c>
+      <c r="D52" t="str">
+        <v>admin@baystatebusinessbrokers.com</v>
+      </c>
+      <c r="E52" t="str">
+        <v>Broker</v>
+      </c>
+      <c r="F52" t="str">
+        <v>Listing 1925 - Geotechnical Drilling &amp; Specialty Foundation Contractor (name not disclosed)</v>
+      </c>
+      <c r="G52" t="str">
+        <v>Other infra (geotechnical drilling / specialty foundation contractor serving infrastructure, transportation, and commercial construction)</v>
+      </c>
+      <c r="H52" t="str">
+        <v>New England</v>
+      </c>
+      <c r="I52" t="str">
+        <v>Unknown (SDE TTM Aug 2026 stated as $806,859; not EBITDA)</v>
+      </c>
+      <c r="J52" t="str">
+        <v>$6,616,639 (TTM Aug 2026)</v>
+      </c>
+      <c r="K52" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="L52" t="str">
+        <v>$2,449,000 (Business Price; Estimated FF&amp;E $1,250,000)</v>
+      </c>
+      <c r="M52" t="str">
+        <v>Capex-heavy construction (specialty geotechnical drilling/foundation contractor; micropiles, earth retention, specialty drilling)</v>
+      </c>
+      <c r="N52" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="O52" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="P52" t="str">
+        <v>BayState Business Brokers</v>
+      </c>
+      <c r="Q52" t="str">
+        <v>Early-access broker blast, 'available to Preferred Buyers for one week'; no CIM/NDA mentioned in email; union specialty contractor, 111 completed projects June 2016-March 2025.</v>
+      </c>
+      <c r="R52">
+        <v>29</v>
+      </c>
+      <c r="S52" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="T52" t="str">
+        <v>Small ($2.4M asking, ~$807K SDE) capex-heavy specialty construction contractor sourced via business broker — well below EBITDA sweet spot and business-model fit despite modest infrastructure/transportation end-market relevance.</v>
+      </c>
+      <c r="U52" t="str">
+        <v>N</v>
+      </c>
+      <c r="V52" t="str">
+        <v>https://outlook.office365.com/owa/?ItemID=AAMkAGJiZDg3MTI0LWFhNzUtNGQzYS1hNWQzLWZlNDVmMmExMzRkNgBGAAAAAAD9u3VVtvqtSpWuAIjP80zoBwB5X058TjLSTIlO61qPMaSdAAAAAAEMAAB5X058TjLSTIlO61qPMaSdAAFpdvOqAAA%3D&amp;exvsurl=1&amp;viewmodel=ReadMessageItem</v>
+      </c>
+      <c r="W52" t="str">
+        <v>New</v>
+      </c>
+      <c r="X52" t="str">
+        <v>&lt;1e2859b3-8b0b-5953-9185-84de083940f7@pds.pdrserv.baystatebusinessbrokers.com&gt;</v>
+      </c>
+      <c r="Y52" t="str">
+        <v>2026-10-12T20:49:21Z</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y51"/>
+  <autoFilter ref="A1:Y52"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Y51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y52"/>
   </ignoredErrors>
 </worksheet>
 </file>